--- a/users.xlsx
+++ b/users.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -494,6 +494,159 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
